--- a/ipo-analysis/companies/bombay-coated-and-special-steels-ltd/BOMBAY_COATED_AND_SPECIA_03_Valuation.xlsx
+++ b/ipo-analysis/companies/bombay-coated-and-special-steels-ltd/BOMBAY_COATED_AND_SPECIA_03_Valuation.xlsx
@@ -1536,7 +1536,7 @@
         </is>
       </c>
       <c r="C18" s="15" t="n">
-        <v>143</v>
+        <v>140.77</v>
       </c>
       <c r="D18" s="21" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="C25" s="15" t="n">
-        <v>1055.707</v>
+        <v>1266.818</v>
       </c>
       <c r="D25" s="21" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         </is>
       </c>
       <c r="C26" s="15" t="n">
-        <v>755.259</v>
+        <v>1055.707</v>
       </c>
       <c r="D26" s="21" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="C27" s="15" t="n">
-        <v>74.092</v>
+        <v>86.09</v>
       </c>
       <c r="D27" s="21" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="C28" s="15" t="n">
-        <v>8.629</v>
+        <v>12.601</v>
       </c>
       <c r="D28" s="21" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="C29" s="15" t="n">
-        <v>28.672</v>
+        <v>30.539</v>
       </c>
       <c r="D29" s="21" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="C30" s="15" t="n">
-        <v>101.992</v>
+        <v>136.615</v>
       </c>
       <c r="D30" s="21" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="C31" s="15" t="n">
-        <v>259.531</v>
+        <v>274.643</v>
       </c>
       <c r="D31" s="21" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="C32" s="15" t="n">
-        <v>179.491</v>
+        <v>232.2</v>
       </c>
       <c r="D32" s="21" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="C33" s="15" t="n">
-        <v>134.406</v>
+        <v>179.491</v>
       </c>
       <c r="D33" s="21" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="C34" s="15" t="n">
-        <v>34.614</v>
+        <v>54.802</v>
       </c>
       <c r="D34" s="21" t="inlineStr">
         <is>
@@ -2148,17 +2148,17 @@
         <v/>
       </c>
       <c r="E67" s="16" t="n">
-        <v>-0.05</v>
+        <v>0.05</v>
       </c>
       <c r="F67" s="16" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="G67" s="16" t="n">
-        <v>0.06</v>
+        <v>0.2</v>
       </c>
       <c r="H67" s="20" t="inlineStr">
         <is>
-          <t>Revenue Rs 590.88 cr -&gt; Rs 755.26 cr -&gt; Rs 1,055.71 cr (33.7% CAGR FY23-25) as Ghiloth (Rajasthan) and Sri City (AP) came up; H1 FY26 revenue Rs 491.51 cr, about 7% below the FY25 run-rate (pp. 44, 279). Capacity 220,506 MTPA with utilisation 46-66% in H1 FY26 (p. 123), so growth needs little new capacity. Neutral: flat FY26, then 8-10% with the appliance (AC, refrigerator) PLI build-out; Bear: FY26 down 5%; Bull: 6% then 10-15%.</t>
+          <t>Revenue Rs 755.26 / 1,055.71 / 1,266.82 cr FY24-26 (+39.8%, +20.0%); Q1 FY27 Rs 397.08 cr, ahead of the FY26 quarterly run-rate of Rs 316.70 cr in the AC season (p. 85). Installed capacity 4.62 lakh MTPA across four plants with 59-64% utilisation in slitting and cut-to-length (pp. 131-132), so growth needs little new capacity. Neutral 12% in FY27 then 8-10%; Bear 5%; Bull 20% then 10-15%.</t>
         </is>
       </c>
     </row>
@@ -2173,7 +2173,7 @@
         <v/>
       </c>
       <c r="E68" s="16" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="F68" s="16" t="n">
         <v>0.1</v>
@@ -2279,11 +2279,11 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="G72" s="16" t="n">
-        <v>0.078</v>
+        <v>0.08</v>
       </c>
       <c r="H72" s="20" t="inlineStr">
         <is>
-          <t>Adjusted EBITDA (issuer KPI, net of other income) Rs 37.65 / 49.17 / 74.09 cr = 6.37% / 6.51% / 7.02% FY23-25 and 7.84% in H1 FY26 (p. 122); reproduces from the P&amp;L. Neutral 7.0% (FY25); Bear 6.4% (FY23-24); Bull 7.8% (H1 FY26).</t>
+          <t>Adjusted EBITDA (issuer KPI, net of other income) Rs 49.17 / 74.09 / 86.09 cr = 6.51% / 7.02% / 6.80% FY24-26 and 8.10% in Q1 FY27 (p. 131); reproduces from the P&amp;L. Neutral 7.0% (three-year level); Bear 6.4%; Bull 8.0% (Q1 FY27).</t>
         </is>
       </c>
     </row>
@@ -2298,17 +2298,17 @@
         <v/>
       </c>
       <c r="E73" s="16" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F73" s="16" t="n">
         <v>0.18</v>
-      </c>
-      <c r="F73" s="16" t="n">
-        <v>0.17</v>
       </c>
       <c r="G73" s="16" t="n">
         <v>0.16</v>
       </c>
       <c r="H73" s="20" t="inlineStr">
         <is>
-          <t>Trade working capital 17.2% / 17.8% / 17.0% of revenue FY23-25 (p. 278); issuer's NWC days 61-73 (p. 123). Neutral 17%.</t>
+          <t>Trade working capital 17.8% / 17.0% / 18.3% of revenue FY24-26 (p. 84); issuer NWC days 66 / 63 / 70 (p. 132). Neutral 18%.</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="H74" s="20" t="inlineStr">
         <is>
-          <t>ROCE 17.89% / 18.60% / 18.78% FY23-25 (p. 123). Neutral terminal ROIC 16%.</t>
+          <t>ROCE 18.60% / 18.78% / 16.40% FY24-26 (p. 132). Neutral terminal ROIC 16%.</t>
         </is>
       </c>
     </row>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="D5" s="20" t="inlineStr">
         <is>
-          <t>Steel processing (slitting, CTL, tubes) - issuer's peer, p. 121</t>
+          <t>Steel processing (slitting, CTL, tubes) - issuer's peer, p. 130</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -3317,7 +3317,7 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>37.76</v>
+        <v>51.17</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>1</v>
@@ -3326,10 +3326,10 @@
       <c r="I5" s="15" t="n"/>
       <c r="J5" s="15" t="n"/>
       <c r="K5" s="15" t="n">
-        <v>2.83</v>
+        <v>3.35</v>
       </c>
       <c r="L5" s="15" t="n">
-        <v>30.84</v>
+        <v>35.85</v>
       </c>
       <c r="M5" s="16" t="n"/>
       <c r="N5" s="13">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="D6" s="20" t="inlineStr">
         <is>
-          <t>Coated steel sheets - issuer's peer, p. 121</t>
+          <t>Coated steel sheets - issuer's peer, p. 130</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -3383,7 +3383,7 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>126.83</v>
+        <v>129.69</v>
       </c>
       <c r="G6" s="15" t="n">
         <v>1</v>
@@ -3392,10 +3392,10 @@
       <c r="I6" s="15" t="n"/>
       <c r="J6" s="15" t="n"/>
       <c r="K6" s="15" t="n">
-        <v>2.1</v>
+        <v>4.18</v>
       </c>
       <c r="L6" s="15" t="n">
-        <v>28.01</v>
+        <v>32.46</v>
       </c>
       <c r="M6" s="16" t="n"/>
       <c r="N6" s="13">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="D7" s="20" t="inlineStr">
         <is>
-          <t>Steel distribution and processing - issuer's peer, p. 121</t>
+          <t>Steel distribution and processing - issuer's peer, p. 130</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -3449,7 +3449,7 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>297.3</v>
+        <v>539</v>
       </c>
       <c r="G7" s="15" t="n">
         <v>1</v>
@@ -3458,10 +3458,10 @@
       <c r="I7" s="15" t="n"/>
       <c r="J7" s="15" t="n"/>
       <c r="K7" s="15" t="n">
-        <v>7.11</v>
+        <v>5.47</v>
       </c>
       <c r="L7" s="15" t="n">
-        <v>84.98999999999999</v>
+        <v>88.86</v>
       </c>
       <c r="M7" s="16" t="n"/>
       <c r="N7" s="13">
